--- a/Bot_Performance_90d.xlsx
+++ b/Bot_Performance_90d.xlsx
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>96166.57000000001</v>
+        <v>95313.02</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>92436.37</v>
+        <v>90769.95</v>
       </c>
     </row>
     <row r="6">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-3833.43</v>
+        <v>-4686.98</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7563.63</v>
+        <v>-9230.049999999999</v>
       </c>
     </row>
     <row r="7">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-3.833</v>
+        <v>-4.687</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-7.564</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="8">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>20</v>
+        <v>28.57</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>20</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="10">
@@ -613,12 +613,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>[0.00, 60.00]</t>
+          <t>[0.00, 57.14]</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>[0.00, 60.00]</t>
+          <t>[0.00, 57.14]</t>
         </is>
       </c>
     </row>
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.082</v>
+        <v>0.094</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.08</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="12">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-0.7771</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>-0.7771</v>
+        <v>-0.6798999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -656,12 +656,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>n=5 -- not computable</t>
+          <t>n=7 -- not computable</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>n=5 -- not computable</t>
+          <t>n=7 -- not computable</t>
         </is>
       </c>
     </row>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>4.18</v>
+        <v>5.18</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>8.220000000000001</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="16">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>0.056</v>
+        <v>0.078</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>0.056</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="18">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>0.078</v>
+        <v>0.109</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.078</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="19">
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>-1058.18</v>
+        <v>-1070.55</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>-1.0694</v>
+        <v>-1.0819</v>
       </c>
     </row>
     <row r="10">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>-1029.3</v>
+        <v>-1046.73</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>-1.0515</v>
+        <v>-1.0694</v>
       </c>
     </row>
     <row r="11">
@@ -1089,22 +1089,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>-1040.16</v>
+        <v>-1018.16</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>-1.0738</v>
+        <v>-1.0515</v>
       </c>
     </row>
     <row r="12">
@@ -1113,70 +1113,70 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>GBPCAD</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>343.49</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0.3585</v>
+      <c r="E12" s="12" t="n">
+        <v>-990.61</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>-1.0339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>-2098.56</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>-2.0986</v>
+      <c r="E13" s="14" t="n">
+        <v>339.91</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0.3585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>-2093.92</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>-2.1388</v>
+      <c r="E14" s="14" t="n">
+        <v>148.44</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>0.156</v>
       </c>
     </row>
     <row r="15">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1197,10 +1197,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>-2014.75</v>
+        <v>-2098.56</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>-2.1029</v>
+        <v>-2.0986</v>
       </c>
     </row>
     <row r="16">
@@ -1209,22 +1209,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-2014.38</v>
+        <v>-2141.1</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>-2.1477</v>
+        <v>-2.187</v>
       </c>
     </row>
     <row r="17">
@@ -1233,22 +1233,118 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>-2048.13</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>-2.1388</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>-1970.68</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>-2.1029</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>GBPCAD</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>-1896.98</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>-2.0677</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>GBPAUD</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>657.98</v>
-      </c>
-      <c r="F17" s="15" t="n">
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>644.12</v>
+      </c>
+      <c r="F20" s="15" t="n">
         <v>0.7169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>GBPAUD</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>281.29</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>0.3109</v>
       </c>
     </row>
   </sheetData>
@@ -2448,13 +2544,13 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>-1049.28</v>
+        <v>-2119.83</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>-1.0493</v>
+        <v>-2.1198</v>
       </c>
     </row>
     <row r="63">
@@ -2555,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>-1058.18</v>
+        <v>-1046.73</v>
       </c>
       <c r="F67" s="13" t="n">
         <v>-1.0694</v>
@@ -2959,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>-1029.3</v>
+        <v>-1018.16</v>
       </c>
       <c r="F87" s="13" t="n">
         <v>-1.0515</v>
@@ -2996,17 +3092,17 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPCAD</t>
         </is>
       </c>
       <c r="D89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>-1040.16</v>
+        <v>-990.61</v>
       </c>
       <c r="F89" s="13" t="n">
-        <v>-1.0738</v>
+        <v>-1.0339</v>
       </c>
     </row>
     <row r="90">
@@ -3164,13 +3260,13 @@
         </is>
       </c>
       <c r="D97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>343.49</v>
+        <v>488.35</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>0.3585</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="98">
@@ -4288,13 +4384,13 @@
         </is>
       </c>
       <c r="D153" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>-2098.56</v>
+        <v>-4239.66</v>
       </c>
       <c r="F153" s="13" t="n">
-        <v>-2.0986</v>
+        <v>-4.2397</v>
       </c>
     </row>
     <row r="154">
@@ -4395,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>-2093.92</v>
+        <v>-2048.13</v>
       </c>
       <c r="F158" s="13" t="n">
         <v>-2.1388</v>
@@ -4799,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>-2014.75</v>
+        <v>-1970.68</v>
       </c>
       <c r="F178" s="13" t="n">
         <v>-2.1029</v>
@@ -4836,17 +4932,17 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPCAD</t>
         </is>
       </c>
       <c r="D180" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>-2014.38</v>
+        <v>-1896.98</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>-2.1477</v>
+        <v>-2.0677</v>
       </c>
     </row>
     <row r="181">
@@ -5004,13 +5100,13 @@
         </is>
       </c>
       <c r="D188" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" s="14" t="n">
-        <v>657.98</v>
+        <v>925.41</v>
       </c>
       <c r="F188" s="15" t="n">
-        <v>0.7169</v>
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -5256,13 +5352,13 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>-1049.28</v>
+        <v>-2119.83</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>-1.0493</v>
+        <v>-2.1198</v>
       </c>
     </row>
     <row r="14">
@@ -5283,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>-1058.18</v>
+        <v>-1046.73</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>-1.0694</v>
@@ -5340,17 +5436,17 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>EURUSD, USDCAD</t>
+          <t>GBPCAD, USDCAD</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>-2069.46</v>
+        <v>-2008.77</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>-2.114</v>
+        <v>-2.0745</v>
       </c>
     </row>
     <row r="18">
@@ -5368,13 +5464,13 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>343.49</v>
+        <v>488.35</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.3585</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="19">
@@ -5552,13 +5648,13 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>-2098.56</v>
+        <v>-4239.66</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>-2.0986</v>
+        <v>-4.2397</v>
       </c>
     </row>
     <row r="28">
@@ -5579,7 +5675,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>-2093.92</v>
+        <v>-2048.13</v>
       </c>
       <c r="F28" s="13" t="n">
         <v>-2.1388</v>
@@ -5636,17 +5732,17 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>EURUSD, USDCAD</t>
+          <t>GBPCAD, USDCAD</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>-4029.13</v>
+        <v>-3867.67</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>-4.2054</v>
+        <v>-4.1272</v>
       </c>
     </row>
     <row r="32">
@@ -5664,13 +5760,13 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>657.98</v>
+        <v>925.41</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>0.7169</v>
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -5796,13 +5892,13 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-2107.46</v>
+        <v>-3166.57</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>-2.1075</v>
+        <v>-3.1666</v>
       </c>
     </row>
     <row r="8">
@@ -5816,17 +5912,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>EURUSD, GBPAUD, USDCAD</t>
+          <t>GBPAUD, GBPCAD, USDCAD</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-1725.97</v>
+        <v>-1520.42</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>-1.7631</v>
+        <v>-1.5701</v>
       </c>
     </row>
     <row r="9">
@@ -5884,13 +5980,13 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>-4192.48</v>
+        <v>-6287.79</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>-4.1925</v>
+        <v>-6.2878</v>
       </c>
     </row>
     <row r="12">
@@ -5904,17 +6000,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>EURUSD, GBPAUD, USDCAD</t>
+          <t>GBPAUD, GBPCAD, USDCAD</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>-3371.14</v>
+        <v>-2942.26</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>-3.5187</v>
+        <v>-3.1397</v>
       </c>
     </row>
   </sheetData>
